--- a/lib/plantillas-aseguradoras/zurich.xlsx
+++ b/lib/plantillas-aseguradoras/zurich.xlsx
@@ -8,7 +8,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'NIT BANCOS'!A1:J174</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'PLANTILLA ENDOSOS'!A5:Z6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'PLANTILLA ENDOSOS'!A5:Z65</definedName>
     <definedName name="Datos_Bancos_Listado">'NIT BANCOS'!$D$2:$D$149</definedName>
     <definedName name="Datos_Bancos_Listado_Nit">'NIT BANCOS'!$D$1:$E$174</definedName>
     <definedName name="Deducibles_Lista_Basico_Demas_Eventos">[1]DEDUCIBLES!$D$2:$D$8</definedName>
@@ -422,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:AC65"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="str">
@@ -531,11 +531,1285 @@
         <v>0</v>
       </c>
     </row>
+    <row r="7">
+      <c r="B7" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="J7">
+        <f>IF(H7="","",IF(I7="","",IF(I7-(H7*$I$2/100)&lt;1,0,I7-(H7*$I$2/100))))</f>
+        <v>0</v>
+      </c>
+      <c r="K7" t="str">
+        <f>IF(L7&lt;119000,"NO GENERA COBRO",L7)</f>
+        <v/>
+      </c>
+      <c r="L7">
+        <f>IF(J7="","",IF(J7=0,0,(J7*$J$2+J7*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="J8">
+        <f>IF(H8="","",IF(I8="","",IF(I8-(H8*$I$2/100)&lt;1,0,I8-(H8*$I$2/100))))</f>
+        <v>0</v>
+      </c>
+      <c r="K8" t="str">
+        <f>IF(L8&lt;119000,"NO GENERA COBRO",L8)</f>
+        <v/>
+      </c>
+      <c r="L8">
+        <f>IF(J8="","",IF(J8=0,0,(J8*$J$2+J8*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="J9">
+        <f>IF(H9="","",IF(I9="","",IF(I9-(H9*$I$2/100)&lt;1,0,I9-(H9*$I$2/100))))</f>
+        <v>0</v>
+      </c>
+      <c r="K9" t="str">
+        <f>IF(L9&lt;119000,"NO GENERA COBRO",L9)</f>
+        <v/>
+      </c>
+      <c r="L9">
+        <f>IF(J9="","",IF(J9=0,0,(J9*$J$2+J9*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="J10">
+        <f>IF(H10="","",IF(I10="","",IF(I10-(H10*$I$2/100)&lt;1,0,I10-(H10*$I$2/100))))</f>
+        <v>0</v>
+      </c>
+      <c r="K10" t="str">
+        <f>IF(L10&lt;119000,"NO GENERA COBRO",L10)</f>
+        <v/>
+      </c>
+      <c r="L10">
+        <f>IF(J10="","",IF(J10=0,0,(J10*$J$2+J10*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="J11">
+        <f>IF(H11="","",IF(I11="","",IF(I11-(H11*$I$2/100)&lt;1,0,I11-(H11*$I$2/100))))</f>
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <f>IF(L11&lt;119000,"NO GENERA COBRO",L11)</f>
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <f>IF(J11="","",IF(J11=0,0,(J11*$J$2+J11*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="J12">
+        <f>IF(H12="","",IF(I12="","",IF(I12-(H12*$I$2/100)&lt;1,0,I12-(H12*$I$2/100))))</f>
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <f>IF(L12&lt;119000,"NO GENERA COBRO",L12)</f>
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <f>IF(J12="","",IF(J12=0,0,(J12*$J$2+J12*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <f>IF(F13="","",VLOOKUP(F13,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <f>IF(H13="","",IF(I13="","",IF(I13-(H13*$I$2/100)&lt;1,0,I13-(H13*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <f>IF(L13&lt;119000,"NO GENERA COBRO",L13)</f>
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <f>IF(J13="","",IF(J13=0,0,(J13*$J$2+J13*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <f>IF(F14="","",VLOOKUP(F14,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J14" t="str">
+        <f>IF(H14="","",IF(I14="","",IF(I14-(H14*$I$2/100)&lt;1,0,I14-(H14*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <f>IF(L14&lt;119000,"NO GENERA COBRO",L14)</f>
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <f>IF(J14="","",IF(J14=0,0,(J14*$J$2+J14*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <f>IF(F15="","",VLOOKUP(F15,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J15" t="str">
+        <f>IF(H15="","",IF(I15="","",IF(I15-(H15*$I$2/100)&lt;1,0,I15-(H15*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <f>IF(L15&lt;119000,"NO GENERA COBRO",L15)</f>
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <f>IF(J15="","",IF(J15=0,0,(J15*$J$2+J15*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <f>IF(F16="","",VLOOKUP(F16,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J16" t="str">
+        <f>IF(H16="","",IF(I16="","",IF(I16-(H16*$I$2/100)&lt;1,0,I16-(H16*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <f>IF(L16&lt;119000,"NO GENERA COBRO",L16)</f>
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <f>IF(J16="","",IF(J16=0,0,(J16*$J$2+J16*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <f>IF(F17="","",VLOOKUP(F17,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J17" t="str">
+        <f>IF(H17="","",IF(I17="","",IF(I17-(H17*$I$2/100)&lt;1,0,I17-(H17*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <f>IF(L17&lt;119000,"NO GENERA COBRO",L17)</f>
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <f>IF(J17="","",IF(J17=0,0,(J17*$J$2+J17*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <f>IF(F18="","",VLOOKUP(F18,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <f>IF(H18="","",IF(I18="","",IF(I18-(H18*$I$2/100)&lt;1,0,I18-(H18*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <f>IF(L18&lt;119000,"NO GENERA COBRO",L18)</f>
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <f>IF(J18="","",IF(J18=0,0,(J18*$J$2+J18*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <f>IF(F19="","",VLOOKUP(F19,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J19" t="str">
+        <f>IF(H19="","",IF(I19="","",IF(I19-(H19*$I$2/100)&lt;1,0,I19-(H19*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <f>IF(L19&lt;119000,"NO GENERA COBRO",L19)</f>
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <f>IF(J19="","",IF(J19=0,0,(J19*$J$2+J19*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <f>IF(F20="","",VLOOKUP(F20,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J20" t="str">
+        <f>IF(H20="","",IF(I20="","",IF(I20-(H20*$I$2/100)&lt;1,0,I20-(H20*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <f>IF(L20&lt;119000,"NO GENERA COBRO",L20)</f>
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <f>IF(J20="","",IF(J20=0,0,(J20*$J$2+J20*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <f>IF(F21="","",VLOOKUP(F21,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J21" t="str">
+        <f>IF(H21="","",IF(I21="","",IF(I21-(H21*$I$2/100)&lt;1,0,I21-(H21*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <f>IF(L21&lt;119000,"NO GENERA COBRO",L21)</f>
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <f>IF(J21="","",IF(J21=0,0,(J21*$J$2+J21*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <f>IF(F22="","",VLOOKUP(F22,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <f>IF(H22="","",IF(I22="","",IF(I22-(H22*$I$2/100)&lt;1,0,I22-(H22*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <f>IF(L22&lt;119000,"NO GENERA COBRO",L22)</f>
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <f>IF(J22="","",IF(J22=0,0,(J22*$J$2+J22*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <f>IF(F23="","",VLOOKUP(F23,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J23" t="str">
+        <f>IF(H23="","",IF(I23="","",IF(I23-(H23*$I$2/100)&lt;1,0,I23-(H23*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <f>IF(L23&lt;119000,"NO GENERA COBRO",L23)</f>
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <f>IF(J23="","",IF(J23=0,0,(J23*$J$2+J23*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <f>IF(F24="","",VLOOKUP(F24,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J24" t="str">
+        <f>IF(H24="","",IF(I24="","",IF(I24-(H24*$I$2/100)&lt;1,0,I24-(H24*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <f>IF(L24&lt;119000,"NO GENERA COBRO",L24)</f>
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <f>IF(J24="","",IF(J24=0,0,(J24*$J$2+J24*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <f>IF(F25="","",VLOOKUP(F25,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J25" t="str">
+        <f>IF(H25="","",IF(I25="","",IF(I25-(H25*$I$2/100)&lt;1,0,I25-(H25*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <f>IF(L25&lt;119000,"NO GENERA COBRO",L25)</f>
+        <v/>
+      </c>
+      <c r="L25" t="str">
+        <f>IF(J25="","",IF(J25=0,0,(J25*$J$2+J25*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <f>IF(F26="","",VLOOKUP(F26,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J26" t="str">
+        <f>IF(H26="","",IF(I26="","",IF(I26-(H26*$I$2/100)&lt;1,0,I26-(H26*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K26" t="str">
+        <f>IF(L26&lt;119000,"NO GENERA COBRO",L26)</f>
+        <v/>
+      </c>
+      <c r="L26" t="str">
+        <f>IF(J26="","",IF(J26=0,0,(J26*$J$2+J26*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <f>IF(F27="","",VLOOKUP(F27,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J27" t="str">
+        <f>IF(H27="","",IF(I27="","",IF(I27-(H27*$I$2/100)&lt;1,0,I27-(H27*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K27" t="str">
+        <f>IF(L27&lt;119000,"NO GENERA COBRO",L27)</f>
+        <v/>
+      </c>
+      <c r="L27" t="str">
+        <f>IF(J27="","",IF(J27=0,0,(J27*$J$2+J27*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <f>IF(F28="","",VLOOKUP(F28,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J28" t="str">
+        <f>IF(H28="","",IF(I28="","",IF(I28-(H28*$I$2/100)&lt;1,0,I28-(H28*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <f>IF(L28&lt;119000,"NO GENERA COBRO",L28)</f>
+        <v/>
+      </c>
+      <c r="L28" t="str">
+        <f>IF(J28="","",IF(J28=0,0,(J28*$J$2+J28*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <f>IF(F29="","",VLOOKUP(F29,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J29" t="str">
+        <f>IF(H29="","",IF(I29="","",IF(I29-(H29*$I$2/100)&lt;1,0,I29-(H29*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K29" t="str">
+        <f>IF(L29&lt;119000,"NO GENERA COBRO",L29)</f>
+        <v/>
+      </c>
+      <c r="L29" t="str">
+        <f>IF(J29="","",IF(J29=0,0,(J29*$J$2+J29*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <f>IF(F30="","",VLOOKUP(F30,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J30" t="str">
+        <f>IF(H30="","",IF(I30="","",IF(I30-(H30*$I$2/100)&lt;1,0,I30-(H30*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K30" t="str">
+        <f>IF(L30&lt;119000,"NO GENERA COBRO",L30)</f>
+        <v/>
+      </c>
+      <c r="L30" t="str">
+        <f>IF(J30="","",IF(J30=0,0,(J30*$J$2+J30*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <f>IF(F31="","",VLOOKUP(F31,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J31" t="str">
+        <f>IF(H31="","",IF(I31="","",IF(I31-(H31*$I$2/100)&lt;1,0,I31-(H31*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K31" t="str">
+        <f>IF(L31&lt;119000,"NO GENERA COBRO",L31)</f>
+        <v/>
+      </c>
+      <c r="L31" t="str">
+        <f>IF(J31="","",IF(J31=0,0,(J31*$J$2+J31*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <f>IF(F32="","",VLOOKUP(F32,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J32" t="str">
+        <f>IF(H32="","",IF(I32="","",IF(I32-(H32*$I$2/100)&lt;1,0,I32-(H32*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K32" t="str">
+        <f>IF(L32&lt;119000,"NO GENERA COBRO",L32)</f>
+        <v/>
+      </c>
+      <c r="L32" t="str">
+        <f>IF(J32="","",IF(J32=0,0,(J32*$J$2+J32*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <f>IF(F33="","",VLOOKUP(F33,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J33" t="str">
+        <f>IF(H33="","",IF(I33="","",IF(I33-(H33*$I$2/100)&lt;1,0,I33-(H33*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K33" t="str">
+        <f>IF(L33&lt;119000,"NO GENERA COBRO",L33)</f>
+        <v/>
+      </c>
+      <c r="L33" t="str">
+        <f>IF(J33="","",IF(J33=0,0,(J33*$J$2+J33*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <f>IF(F34="","",VLOOKUP(F34,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J34" t="str">
+        <f>IF(H34="","",IF(I34="","",IF(I34-(H34*$I$2/100)&lt;1,0,I34-(H34*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K34" t="str">
+        <f>IF(L34&lt;119000,"NO GENERA COBRO",L34)</f>
+        <v/>
+      </c>
+      <c r="L34" t="str">
+        <f>IF(J34="","",IF(J34=0,0,(J34*$J$2+J34*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G35" t="str">
+        <f>IF(F35="","",VLOOKUP(F35,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J35" t="str">
+        <f>IF(H35="","",IF(I35="","",IF(I35-(H35*$I$2/100)&lt;1,0,I35-(H35*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K35" t="str">
+        <f>IF(L35&lt;119000,"NO GENERA COBRO",L35)</f>
+        <v/>
+      </c>
+      <c r="L35" t="str">
+        <f>IF(J35="","",IF(J35=0,0,(J35*$J$2+J35*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G36" t="str">
+        <f>IF(F36="","",VLOOKUP(F36,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J36" t="str">
+        <f>IF(H36="","",IF(I36="","",IF(I36-(H36*$I$2/100)&lt;1,0,I36-(H36*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K36" t="str">
+        <f>IF(L36&lt;119000,"NO GENERA COBRO",L36)</f>
+        <v/>
+      </c>
+      <c r="L36" t="str">
+        <f>IF(J36="","",IF(J36=0,0,(J36*$J$2+J36*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <f>IF(F37="","",VLOOKUP(F37,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J37" t="str">
+        <f>IF(H37="","",IF(I37="","",IF(I37-(H37*$I$2/100)&lt;1,0,I37-(H37*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K37" t="str">
+        <f>IF(L37&lt;119000,"NO GENERA COBRO",L37)</f>
+        <v/>
+      </c>
+      <c r="L37" t="str">
+        <f>IF(J37="","",IF(J37=0,0,(J37*$J$2+J37*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <f>IF(F38="","",VLOOKUP(F38,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J38" t="str">
+        <f>IF(H38="","",IF(I38="","",IF(I38-(H38*$I$2/100)&lt;1,0,I38-(H38*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K38" t="str">
+        <f>IF(L38&lt;119000,"NO GENERA COBRO",L38)</f>
+        <v/>
+      </c>
+      <c r="L38" t="str">
+        <f>IF(J38="","",IF(J38=0,0,(J38*$J$2+J38*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <f>IF(F39="","",VLOOKUP(F39,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J39" t="str">
+        <f>IF(H39="","",IF(I39="","",IF(I39-(H39*$I$2/100)&lt;1,0,I39-(H39*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K39" t="str">
+        <f>IF(L39&lt;119000,"NO GENERA COBRO",L39)</f>
+        <v/>
+      </c>
+      <c r="L39" t="str">
+        <f>IF(J39="","",IF(J39=0,0,(J39*$J$2+J39*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <f>IF(F40="","",VLOOKUP(F40,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J40" t="str">
+        <f>IF(H40="","",IF(I40="","",IF(I40-(H40*$I$2/100)&lt;1,0,I40-(H40*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K40" t="str">
+        <f>IF(L40&lt;119000,"NO GENERA COBRO",L40)</f>
+        <v/>
+      </c>
+      <c r="L40" t="str">
+        <f>IF(J40="","",IF(J40=0,0,(J40*$J$2+J40*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G41" t="str">
+        <f>IF(F41="","",VLOOKUP(F41,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J41" t="str">
+        <f>IF(H41="","",IF(I41="","",IF(I41-(H41*$I$2/100)&lt;1,0,I41-(H41*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K41" t="str">
+        <f>IF(L41&lt;119000,"NO GENERA COBRO",L41)</f>
+        <v/>
+      </c>
+      <c r="L41" t="str">
+        <f>IF(J41="","",IF(J41=0,0,(J41*$J$2+J41*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G42" t="str">
+        <f>IF(F42="","",VLOOKUP(F42,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J42" t="str">
+        <f>IF(H42="","",IF(I42="","",IF(I42-(H42*$I$2/100)&lt;1,0,I42-(H42*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K42" t="str">
+        <f>IF(L42&lt;119000,"NO GENERA COBRO",L42)</f>
+        <v/>
+      </c>
+      <c r="L42" t="str">
+        <f>IF(J42="","",IF(J42=0,0,(J42*$J$2+J42*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <f>IF(F43="","",VLOOKUP(F43,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J43" t="str">
+        <f>IF(H43="","",IF(I43="","",IF(I43-(H43*$I$2/100)&lt;1,0,I43-(H43*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K43" t="str">
+        <f>IF(L43&lt;119000,"NO GENERA COBRO",L43)</f>
+        <v/>
+      </c>
+      <c r="L43" t="str">
+        <f>IF(J43="","",IF(J43=0,0,(J43*$J$2+J43*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <f>IF(F44="","",VLOOKUP(F44,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J44" t="str">
+        <f>IF(H44="","",IF(I44="","",IF(I44-(H44*$I$2/100)&lt;1,0,I44-(H44*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K44" t="str">
+        <f>IF(L44&lt;119000,"NO GENERA COBRO",L44)</f>
+        <v/>
+      </c>
+      <c r="L44" t="str">
+        <f>IF(J44="","",IF(J44=0,0,(J44*$J$2+J44*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G45" t="str">
+        <f>IF(F45="","",VLOOKUP(F45,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J45" t="str">
+        <f>IF(H45="","",IF(I45="","",IF(I45-(H45*$I$2/100)&lt;1,0,I45-(H45*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K45" t="str">
+        <f>IF(L45&lt;119000,"NO GENERA COBRO",L45)</f>
+        <v/>
+      </c>
+      <c r="L45" t="str">
+        <f>IF(J45="","",IF(J45=0,0,(J45*$J$2+J45*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G46" t="str">
+        <f>IF(F46="","",VLOOKUP(F46,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J46" t="str">
+        <f>IF(H46="","",IF(I46="","",IF(I46-(H46*$I$2/100)&lt;1,0,I46-(H46*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K46" t="str">
+        <f>IF(L46&lt;119000,"NO GENERA COBRO",L46)</f>
+        <v/>
+      </c>
+      <c r="L46" t="str">
+        <f>IF(J46="","",IF(J46=0,0,(J46*$J$2+J46*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G47" t="str">
+        <f>IF(F47="","",VLOOKUP(F47,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J47" t="str">
+        <f>IF(H47="","",IF(I47="","",IF(I47-(H47*$I$2/100)&lt;1,0,I47-(H47*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K47" t="str">
+        <f>IF(L47&lt;119000,"NO GENERA COBRO",L47)</f>
+        <v/>
+      </c>
+      <c r="L47" t="str">
+        <f>IF(J47="","",IF(J47=0,0,(J47*$J$2+J47*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G48" t="str">
+        <f>IF(F48="","",VLOOKUP(F48,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J48" t="str">
+        <f>IF(H48="","",IF(I48="","",IF(I48-(H48*$I$2/100)&lt;1,0,I48-(H48*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K48" t="str">
+        <f>IF(L48&lt;119000,"NO GENERA COBRO",L48)</f>
+        <v/>
+      </c>
+      <c r="L48" t="str">
+        <f>IF(J48="","",IF(J48=0,0,(J48*$J$2+J48*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G49" t="str">
+        <f>IF(F49="","",VLOOKUP(F49,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J49" t="str">
+        <f>IF(H49="","",IF(I49="","",IF(I49-(H49*$I$2/100)&lt;1,0,I49-(H49*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K49" t="str">
+        <f>IF(L49&lt;119000,"NO GENERA COBRO",L49)</f>
+        <v/>
+      </c>
+      <c r="L49" t="str">
+        <f>IF(J49="","",IF(J49=0,0,(J49*$J$2+J49*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G50" t="str">
+        <f>IF(F50="","",VLOOKUP(F50,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J50" t="str">
+        <f>IF(H50="","",IF(I50="","",IF(I50-(H50*$I$2/100)&lt;1,0,I50-(H50*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K50" t="str">
+        <f>IF(L50&lt;119000,"NO GENERA COBRO",L50)</f>
+        <v/>
+      </c>
+      <c r="L50" t="str">
+        <f>IF(J50="","",IF(J50=0,0,(J50*$J$2+J50*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G51" t="str">
+        <f>IF(F51="","",VLOOKUP(F51,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J51" t="str">
+        <f>IF(H51="","",IF(I51="","",IF(I51-(H51*$I$2/100)&lt;1,0,I51-(H51*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K51" t="str">
+        <f>IF(L51&lt;119000,"NO GENERA COBRO",L51)</f>
+        <v/>
+      </c>
+      <c r="L51" t="str">
+        <f>IF(J51="","",IF(J51=0,0,(J51*$J$2+J51*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G52" t="str">
+        <f>IF(F52="","",VLOOKUP(F52,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J52" t="str">
+        <f>IF(H52="","",IF(I52="","",IF(I52-(H52*$I$2/100)&lt;1,0,I52-(H52*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K52" t="str">
+        <f>IF(L52&lt;119000,"NO GENERA COBRO",L52)</f>
+        <v/>
+      </c>
+      <c r="L52" t="str">
+        <f>IF(J52="","",IF(J52=0,0,(J52*$J$2+J52*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G53" t="str">
+        <f>IF(F53="","",VLOOKUP(F53,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J53" t="str">
+        <f>IF(H53="","",IF(I53="","",IF(I53-(H53*$I$2/100)&lt;1,0,I53-(H53*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K53" t="str">
+        <f>IF(L53&lt;119000,"NO GENERA COBRO",L53)</f>
+        <v/>
+      </c>
+      <c r="L53" t="str">
+        <f>IF(J53="","",IF(J53=0,0,(J53*$J$2+J53*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G54" t="str">
+        <f>IF(F54="","",VLOOKUP(F54,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J54" t="str">
+        <f>IF(H54="","",IF(I54="","",IF(I54-(H54*$I$2/100)&lt;1,0,I54-(H54*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K54" t="str">
+        <f>IF(L54&lt;119000,"NO GENERA COBRO",L54)</f>
+        <v/>
+      </c>
+      <c r="L54" t="str">
+        <f>IF(J54="","",IF(J54=0,0,(J54*$J$2+J54*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G55" t="str">
+        <f>IF(F55="","",VLOOKUP(F55,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J55" t="str">
+        <f>IF(H55="","",IF(I55="","",IF(I55-(H55*$I$2/100)&lt;1,0,I55-(H55*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K55" t="str">
+        <f>IF(L55&lt;119000,"NO GENERA COBRO",L55)</f>
+        <v/>
+      </c>
+      <c r="L55" t="str">
+        <f>IF(J55="","",IF(J55=0,0,(J55*$J$2+J55*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G56" t="str">
+        <f>IF(F56="","",VLOOKUP(F56,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J56" t="str">
+        <f>IF(H56="","",IF(I56="","",IF(I56-(H56*$I$2/100)&lt;1,0,I56-(H56*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K56" t="str">
+        <f>IF(L56&lt;119000,"NO GENERA COBRO",L56)</f>
+        <v/>
+      </c>
+      <c r="L56" t="str">
+        <f>IF(J56="","",IF(J56=0,0,(J56*$J$2+J56*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <f>IF(F57="","",VLOOKUP(F57,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J57" t="str">
+        <f>IF(H57="","",IF(I57="","",IF(I57-(H57*$I$2/100)&lt;1,0,I57-(H57*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K57" t="str">
+        <f>IF(L57&lt;119000,"NO GENERA COBRO",L57)</f>
+        <v/>
+      </c>
+      <c r="L57" t="str">
+        <f>IF(J57="","",IF(J57=0,0,(J57*$J$2+J57*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <f>IF(F58="","",VLOOKUP(F58,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J58" t="str">
+        <f>IF(H58="","",IF(I58="","",IF(I58-(H58*$I$2/100)&lt;1,0,I58-(H58*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K58" t="str">
+        <f>IF(L58&lt;119000,"NO GENERA COBRO",L58)</f>
+        <v/>
+      </c>
+      <c r="L58" t="str">
+        <f>IF(J58="","",IF(J58=0,0,(J58*$J$2+J58*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G59" t="str">
+        <f>IF(F59="","",VLOOKUP(F59,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J59" t="str">
+        <f>IF(H59="","",IF(I59="","",IF(I59-(H59*$I$2/100)&lt;1,0,I59-(H59*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K59" t="str">
+        <f>IF(L59&lt;119000,"NO GENERA COBRO",L59)</f>
+        <v/>
+      </c>
+      <c r="L59" t="str">
+        <f>IF(J59="","",IF(J59=0,0,(J59*$J$2+J59*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G60" t="str">
+        <f>IF(F60="","",VLOOKUP(F60,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J60" t="str">
+        <f>IF(H60="","",IF(I60="","",IF(I60-(H60*$I$2/100)&lt;1,0,I60-(H60*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K60" t="str">
+        <f>IF(L60&lt;119000,"NO GENERA COBRO",L60)</f>
+        <v/>
+      </c>
+      <c r="L60" t="str">
+        <f>IF(J60="","",IF(J60=0,0,(J60*$J$2+J60*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G61" t="str">
+        <f>IF(F61="","",VLOOKUP(F61,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J61" t="str">
+        <f>IF(H61="","",IF(I61="","",IF(I61-(H61*$I$2/100)&lt;1,0,I61-(H61*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K61" t="str">
+        <f>IF(L61&lt;119000,"NO GENERA COBRO",L61)</f>
+        <v/>
+      </c>
+      <c r="L61" t="str">
+        <f>IF(J61="","",IF(J61=0,0,(J61*$J$2+J61*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G62" t="str">
+        <f>IF(F62="","",VLOOKUP(F62,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J62" t="str">
+        <f>IF(H62="","",IF(I62="","",IF(I62-(H62*$I$2/100)&lt;1,0,I62-(H62*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K62" t="str">
+        <f>IF(L62&lt;119000,"NO GENERA COBRO",L62)</f>
+        <v/>
+      </c>
+      <c r="L62" t="str">
+        <f>IF(J62="","",IF(J62=0,0,(J62*$J$2+J62*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G63" t="str">
+        <f>IF(F63="","",VLOOKUP(F63,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J63" t="str">
+        <f>IF(H63="","",IF(I63="","",IF(I63-(H63*$I$2/100)&lt;1,0,I63-(H63*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K63" t="str">
+        <f>IF(L63&lt;119000,"NO GENERA COBRO",L63)</f>
+        <v/>
+      </c>
+      <c r="L63" t="str">
+        <f>IF(J63="","",IF(J63=0,0,(J63*$J$2+J63*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G64" t="str">
+        <f>IF(F64="","",VLOOKUP(F64,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J64" t="str">
+        <f>IF(H64="","",IF(I64="","",IF(I64-(H64*$I$2/100)&lt;1,0,I64-(H64*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K64" t="str">
+        <f>IF(L64&lt;119000,"NO GENERA COBRO",L64)</f>
+        <v/>
+      </c>
+      <c r="L64" t="str">
+        <f>IF(J64="","",IF(J64=0,0,(J64*$J$2+J64*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="str">
+        <f>IF($B$2="","",$B$2)</f>
+        <v/>
+      </c>
+      <c r="G65" t="str">
+        <f>IF(F65="","",VLOOKUP(F65,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J65" t="str">
+        <f>IF(H65="","",IF(I65="","",IF(I65-(H65*$I$2/100)&lt;1,0,I65-(H65*$I$2/100))))</f>
+        <v/>
+      </c>
+      <c r="K65" t="str">
+        <f>IF(L65&lt;119000,"NO GENERA COBRO",L65)</f>
+        <v/>
+      </c>
+      <c r="L65" t="str">
+        <f>IF(J65="","",IF(J65=0,0,(J65*$J$2+J65*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:Z6"/>
+  <autoFilter ref="A5:Z65"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AC6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AC65"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/lib/plantillas-aseguradoras/zurich.xlsx
+++ b/lib/plantillas-aseguradoras/zurich.xlsx
@@ -44,7 +44,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="14">
+  <numFmts count="15">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(&quot;$&quot;\ * #,##0.00_);_(&quot;$&quot;\ * \(#,##0.00\);_(&quot;$&quot;\ * &quot;-&quot;??_);_(@_)"/>
@@ -59,6 +59,7 @@
     <numFmt numFmtId="174" formatCode="[$$-240A]#,##0.00;[Red]&quot;(&quot;[$$-240A]#,##0.00&quot;)&quot;"/>
     <numFmt numFmtId="175" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="&quot;$&quot;\ #,##0_);[Red]\(&quot;$&quot;\ #,##0\)"/>
+    <numFmt numFmtId="177" formatCode="#,##0.00;[Red]#,##0.00"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -514,9 +515,17 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B6" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
+      </c>
+      <c r="G6">
+        <f>IF(F6="","",VLOOKUP(F6,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v>0</v>
       </c>
       <c r="J6">
         <f>IF(H6="","",IF(I6="","",IF(I6-(H6*$I$2/100)&lt;1,0,I6-(H6*$I$2/100))))</f>
@@ -532,114 +541,166 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B7" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
       </c>
-      <c r="J7">
+      <c r="G7" t="str">
+        <f>IF(F7="","",VLOOKUP(F7,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J7" t="str">
         <f>IF(H7="","",IF(I7="","",IF(I7-(H7*$I$2/100)&lt;1,0,I7-(H7*$I$2/100))))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="K7" t="str">
         <f>IF(L7&lt;119000,"NO GENERA COBRO",L7)</f>
         <v/>
       </c>
-      <c r="L7">
+      <c r="L7" t="str">
         <f>IF(J7="","",IF(J7=0,0,(J7*$J$2+J7*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="8">
+      <c r="A8">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B8" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
       </c>
-      <c r="J8">
+      <c r="G8" t="str">
+        <f>IF(F8="","",VLOOKUP(F8,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J8" t="str">
         <f>IF(H8="","",IF(I8="","",IF(I8-(H8*$I$2/100)&lt;1,0,I8-(H8*$I$2/100))))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="K8" t="str">
         <f>IF(L8&lt;119000,"NO GENERA COBRO",L8)</f>
         <v/>
       </c>
-      <c r="L8">
+      <c r="L8" t="str">
         <f>IF(J8="","",IF(J8=0,0,(J8*$J$2+J8*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="9">
+      <c r="A9">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B9" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
       </c>
-      <c r="J9">
+      <c r="G9" t="str">
+        <f>IF(F9="","",VLOOKUP(F9,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J9" t="str">
         <f>IF(H9="","",IF(I9="","",IF(I9-(H9*$I$2/100)&lt;1,0,I9-(H9*$I$2/100))))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="K9" t="str">
         <f>IF(L9&lt;119000,"NO GENERA COBRO",L9)</f>
         <v/>
       </c>
-      <c r="L9">
+      <c r="L9" t="str">
         <f>IF(J9="","",IF(J9=0,0,(J9*$J$2+J9*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="10">
+      <c r="A10">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B10" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
       </c>
-      <c r="J10">
+      <c r="G10" t="str">
+        <f>IF(F10="","",VLOOKUP(F10,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J10" t="str">
         <f>IF(H10="","",IF(I10="","",IF(I10-(H10*$I$2/100)&lt;1,0,I10-(H10*$I$2/100))))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="K10" t="str">
         <f>IF(L10&lt;119000,"NO GENERA COBRO",L10)</f>
         <v/>
       </c>
-      <c r="L10">
+      <c r="L10" t="str">
         <f>IF(J10="","",IF(J10=0,0,(J10*$J$2+J10*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="11">
+      <c r="A11">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B11" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
       </c>
-      <c r="J11">
+      <c r="G11" t="str">
+        <f>IF(F11="","",VLOOKUP(F11,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J11" t="str">
         <f>IF(H11="","",IF(I11="","",IF(I11-(H11*$I$2/100)&lt;1,0,I11-(H11*$I$2/100))))</f>
-        <v>0</v>
-      </c>
-      <c r="K11">
+        <v/>
+      </c>
+      <c r="K11" t="str">
         <f>IF(L11&lt;119000,"NO GENERA COBRO",L11)</f>
-        <v>0</v>
-      </c>
-      <c r="L11">
+        <v/>
+      </c>
+      <c r="L11" t="str">
         <f>IF(J11="","",IF(J11=0,0,(J11*$J$2+J11*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="12">
+      <c r="A12">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B12" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
       </c>
-      <c r="J12">
+      <c r="G12" t="str">
+        <f>IF(F12="","",VLOOKUP(F12,Datos_Bancos_Listado_Nit,2,0))</f>
+        <v/>
+      </c>
+      <c r="J12" t="str">
         <f>IF(H12="","",IF(I12="","",IF(I12-(H12*$I$2/100)&lt;1,0,I12-(H12*$I$2/100))))</f>
-        <v>0</v>
-      </c>
-      <c r="K12">
+        <v/>
+      </c>
+      <c r="K12" t="str">
         <f>IF(L12&lt;119000,"NO GENERA COBRO",L12)</f>
-        <v>0</v>
-      </c>
-      <c r="L12">
+        <v/>
+      </c>
+      <c r="L12" t="str">
         <f>IF(J12="","",IF(J12=0,0,(J12*$J$2+J12*$K$2*$J$3)/$L$2*$L$3)*1.19/10)</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="13">
+      <c r="A13">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B13" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -662,6 +723,10 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B14" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -684,6 +749,10 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B15" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -706,6 +775,10 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B16" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -728,6 +801,10 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B17" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -750,6 +827,10 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B18" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -772,6 +853,10 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B19" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -794,6 +879,10 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B20" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -816,6 +905,10 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B21" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -838,6 +931,10 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B22" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -860,6 +957,10 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B23" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -882,6 +983,10 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B24" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -904,6 +1009,10 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B25" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -926,6 +1035,10 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B26" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -948,6 +1061,10 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B27" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -970,6 +1087,10 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B28" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -992,6 +1113,10 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B29" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -1014,6 +1139,10 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B30" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -1036,6 +1165,10 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B31" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -1058,6 +1191,10 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B32" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -1080,6 +1217,10 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B33" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -1102,6 +1243,10 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B34" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -1124,6 +1269,10 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B35" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -1146,6 +1295,10 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B36" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -1168,6 +1321,10 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B37" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -1190,6 +1347,10 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B38" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -1212,6 +1373,10 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B39" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -1234,6 +1399,10 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B40" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -1256,6 +1425,10 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B41" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -1278,6 +1451,10 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B42" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -1300,6 +1477,10 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B43" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -1322,6 +1503,10 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B44" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -1344,6 +1529,10 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B45" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -1366,6 +1555,10 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B46" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -1388,6 +1581,10 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B47" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -1410,6 +1607,10 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B48" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -1432,6 +1633,10 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B49" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -1454,6 +1659,10 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B50" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -1476,6 +1685,10 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B51" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -1498,6 +1711,10 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B52" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -1520,6 +1737,10 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B53" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -1542,6 +1763,10 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B54" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -1564,6 +1789,10 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B55" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -1586,6 +1815,10 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B56" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -1608,6 +1841,10 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B57" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -1630,6 +1867,10 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B58" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -1652,6 +1893,10 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B59" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -1674,6 +1919,10 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B60" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -1696,6 +1945,10 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B61" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -1718,6 +1971,10 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B62" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -1740,6 +1997,10 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B63" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -1762,6 +2023,10 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B64" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -1784,6 +2049,10 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65">
+        <f>ROW()-5</f>
+        <v>0</v>
+      </c>
       <c r="B65" t="str">
         <f>IF($B$2="","",$B$2)</f>
         <v/>
@@ -2039,14 +2308,14 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>BANCO COLPATRIA RED MULTIBANCA S.A.</v>
+        <v>DAVIbank</v>
       </c>
       <c r="C9">
         <v>8600345941</v>
       </c>
       <c r="D9" t="str">
         <f>+B9</f>
-        <v>BANCO COLPATRIA RED MULTIBANCA S.A.</v>
+        <v>DAVIbank</v>
       </c>
       <c r="E9">
         <f>+C9</f>
